--- a/data/trans_orig/Q5401-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2007</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>37338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>53849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86606</t>
+          <t>87594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>51699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79784</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121525</t>
+          <t>122010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164311</t>
+          <t>164892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183098</t>
+          <t>184092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235223</t>
+          <t>232966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264808</t>
+          <t>265507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>297049</t>
+          <t>296532</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>379650</t>
+          <t>380624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>423360</t>
+          <t>425811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>654168</t>
+          <t>658574</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711210</t>
+          <t>709401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13858</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>67894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80948</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113392</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132976</t>
+          <t>132975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>55736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97913</t>
+          <t>97972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179946</t>
+          <t>182362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213871</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269161</t>
+          <t>269046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>370725</t>
+          <t>369604</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>405765</t>
+          <t>404284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>444617</t>
+          <t>442243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>494833</t>
+          <t>492768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>827939</t>
+          <t>826571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>888554</t>
+          <t>889077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2012</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36659</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73215</t>
+          <t>73481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107667</t>
+          <t>107841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117051</t>
+          <t>116532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163802</t>
+          <t>163492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53659</t>
+          <t>54036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86640</t>
+          <t>86435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117358</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157484</t>
+          <t>156540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176412</t>
+          <t>180257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231315</t>
+          <t>233497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>276238</t>
+          <t>273015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313499</t>
+          <t>313604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385214</t>
+          <t>383372</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>432769</t>
+          <t>435357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>674990</t>
+          <t>672273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>742516</t>
+          <t>735416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9160</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89796</t>
+          <t>89388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106887</t>
+          <t>107121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>58175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73304</t>
+          <t>74016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154411</t>
+          <t>154013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176693</t>
+          <t>176562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37420</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46820</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>76708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113007</t>
+          <t>114803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>122745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171884</t>
+          <t>173985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67618</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104614</t>
+          <t>102908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130658</t>
+          <t>130355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174251</t>
+          <t>175319</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210788</t>
+          <t>207304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263427</t>
+          <t>265375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>398943</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>441934</t>
+          <t>442326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>467346</t>
+          <t>466607</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>518684</t>
+          <t>520172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>880547</t>
+          <t>877858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>949445</t>
+          <t>948099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2016</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26532</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47960</t>
+          <t>47491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,82 +4858,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>48729</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35506</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>65767</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>85023</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>68114</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>105450</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>7,5%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>48729</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36120</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66000</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>85023</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>68850</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>107033</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41855</t>
+          <t>40689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68193</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113936</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159906</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161953</t>
+          <t>163569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213325</t>
+          <t>213279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248737</t>
+          <t>248577</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>279186</t>
+          <t>279524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>345283</t>
+          <t>346579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>393831</t>
+          <t>394258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>606201</t>
+          <t>606771</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>663796</t>
+          <t>664030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32791</t>
+          <t>32724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58573</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>41949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70885</t>
+          <t>72101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165087</t>
+          <t>165008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180905</t>
+          <t>181022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129501</t>
+          <t>127487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155283</t>
+          <t>155350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300328</t>
+          <t>300343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331318</t>
+          <t>331029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70253</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>34919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>59724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77670</t>
+          <t>77597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116718</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54092</t>
+          <t>53094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83598</t>
+          <t>81414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158775</t>
+          <t>158075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211904</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219897</t>
+          <t>221486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282458</t>
+          <t>282003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>455854</t>
+          <t>459253</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>492466</t>
+          <t>494050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>513989</t>
+          <t>514407</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>572257</t>
+          <t>570039</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>984654</t>
+          <t>982003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1052821</t>
+          <t>1048529</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2023</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>101967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109792</t>
+          <t>108024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>137460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>39598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59560</t>
+          <t>58749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120057</t>
+          <t>119527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147218</t>
+          <t>147300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167048</t>
+          <t>165098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200919</t>
+          <t>199304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172613</t>
+          <t>173043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195631</t>
+          <t>196073</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262722</t>
+          <t>262378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>292921</t>
+          <t>293693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>445159</t>
+          <t>443854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>483090</t>
+          <t>482807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30457</t>
+          <t>31822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>76909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97923</t>
+          <t>97417</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225672</t>
+          <t>226273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243991</t>
+          <t>244453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>361102</t>
+          <t>360928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>438467</t>
+          <t>437596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>602223</t>
+          <t>602405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>689269</t>
+          <t>686139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96089</t>
+          <t>96478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53545</t>
+          <t>53432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>62472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142273</t>
+          <t>142245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156669</t>
+          <t>157064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>59526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128933</t>
+          <t>130422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175746</t>
+          <t>177440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71746</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100955</t>
+          <t>99141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95570</t>
+          <t>94671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>235250</t>
+          <t>237544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183973</t>
+          <t>171596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316374</t>
+          <t>314814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>494883</t>
+          <t>495252</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>528246</t>
+          <t>527001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>666625</t>
+          <t>664739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>880319</t>
+          <t>882766</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1188478</t>
+          <t>1187636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397459</t>
+          <t>1405970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5401-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>30117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>58279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53849</t>
+          <t>54929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87594</t>
+          <t>88634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80037</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122010</t>
+          <t>121699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164892</t>
+          <t>164004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184092</t>
+          <t>181655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232966</t>
+          <t>232714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265507</t>
+          <t>264638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>296532</t>
+          <t>296903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>380624</t>
+          <t>379151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>425811</t>
+          <t>424699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>658574</t>
+          <t>657318</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>709401</t>
+          <t>711837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,08%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>68821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80930</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>114595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132975</t>
+          <t>133205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36594</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62026</t>
+          <t>62533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97972</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>103252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182362</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214501</t>
+          <t>216785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269046</t>
+          <t>270684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>369604</t>
+          <t>367864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>404284</t>
+          <t>405105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>442243</t>
+          <t>444283</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>492768</t>
+          <t>493120</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>826571</t>
+          <t>829621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>889077</t>
+          <t>888570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>37288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73481</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>108803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116532</t>
+          <t>118835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163492</t>
+          <t>162890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>88580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116003</t>
+          <t>114761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>156608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180257</t>
+          <t>179801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233497</t>
+          <t>229590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273015</t>
+          <t>276719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>313604</t>
+          <t>314134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>383372</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435357</t>
+          <t>436342</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>672273</t>
+          <t>673714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>735416</t>
+          <t>737351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>23573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38962</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89388</t>
+          <t>89945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107121</t>
+          <t>106776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58175</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74016</t>
+          <t>73688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154013</t>
+          <t>154200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176562</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76708</t>
+          <t>77786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114803</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122745</t>
+          <t>125837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173985</t>
+          <t>173157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66302</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102908</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130355</t>
+          <t>129539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175319</t>
+          <t>173936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207304</t>
+          <t>208110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265375</t>
+          <t>267239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>397822</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>442326</t>
+          <t>443466</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>466607</t>
+          <t>466948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>520172</t>
+          <t>517208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>877858</t>
+          <t>882381</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>948099</t>
+          <t>950287</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47491</t>
+          <t>48763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35506</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>65854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>67473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105450</t>
+          <t>103259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114411</t>
+          <t>113851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158867</t>
+          <t>159175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163569</t>
+          <t>161053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213279</t>
+          <t>215512</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248577</t>
+          <t>248271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>279524</t>
+          <t>278754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>346579</t>
+          <t>345234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>394258</t>
+          <t>394467</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>606771</t>
+          <t>608080</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>664030</t>
+          <t>665559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60587</t>
+          <t>59815</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41949</t>
+          <t>40297</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72101</t>
+          <t>69763</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165008</t>
+          <t>165070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181022</t>
+          <t>180816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127487</t>
+          <t>128259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155350</t>
+          <t>154542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300343</t>
+          <t>300275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331029</t>
+          <t>331146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>57132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70649</t>
+          <t>70474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34919</t>
+          <t>34620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>59324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>66321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>76921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>114376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53094</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81414</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158075</t>
+          <t>155841</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211595</t>
+          <t>209386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221486</t>
+          <t>220154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282003</t>
+          <t>280514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>459253</t>
+          <t>457430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>494050</t>
+          <t>492303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>514407</t>
+          <t>515173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>570039</t>
+          <t>569133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>982003</t>
+          <t>983320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1048529</t>
+          <t>1050231</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>35740</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>88897</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>83326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>109065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>123035</t>
+          <t>131161</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108024</t>
+          <t>115394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>147034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49104</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>63229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>133143</t>
+          <t>143326</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119527</t>
+          <t>128898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147300</t>
+          <t>157863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>182246</t>
+          <t>195418</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165098</t>
+          <t>175519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199304</t>
+          <t>212942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>184681</t>
+          <t>200800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173043</t>
+          <t>187557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>196073</t>
+          <t>213742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>278694</t>
+          <t>300034</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262378</t>
+          <t>283831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>293693</t>
+          <t>317149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>463374</t>
+          <t>500834</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>443854</t>
+          <t>479414</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>482807</t>
+          <t>524262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>267923</t>
+          <t>288632</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267923</t>
+          <t>288632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267923</t>
+          <t>288632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>768656</t>
+          <t>827413</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>768656</t>
+          <t>827413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>768656</t>
+          <t>827413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -7462,27 +7462,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39472</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76909</t>
+          <t>55017</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>65966</t>
+          <t>75275</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>62467</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>97417</t>
+          <t>88121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>235967</t>
+          <t>262678</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226273</t>
+          <t>252315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244453</t>
+          <t>271120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>406556</t>
+          <t>220718</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>360928</t>
+          <t>210714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>437596</t>
+          <t>230065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>642523</t>
+          <t>483396</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>602405</t>
+          <t>469635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>686139</t>
+          <t>498118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455174</t>
+          <t>277077</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455174</t>
+          <t>277077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455174</t>
+          <t>277077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728431</t>
+          <t>580902</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728431</t>
+          <t>580902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728431</t>
+          <t>580902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91747</t>
+          <t>104188</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85252</t>
+          <t>97228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96478</t>
+          <t>109612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53432</t>
+          <t>62483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62472</t>
+          <t>72614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>150149</t>
+          <t>172547</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142245</t>
+          <t>164496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157064</t>
+          <t>179963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>41118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59526</t>
+          <t>63719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>99025</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51243</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130422</t>
+          <t>121797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147872</t>
+          <t>159054</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99908</t>
+          <t>140744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177440</t>
+          <t>178795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84925</t>
+          <t>92246</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72455</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>107229</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>184555</t>
+          <t>201974</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94671</t>
+          <t>182290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237544</t>
+          <t>219715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>269479</t>
+          <t>294221</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171596</t>
+          <t>271857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314814</t>
+          <t>319069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>512395</t>
+          <t>567666</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>495252</t>
+          <t>549457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>527001</t>
+          <t>584820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>743651</t>
+          <t>589110</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>664739</t>
+          <t>568009</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>882766</t>
+          <t>609837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1256046</t>
+          <t>1156776</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1187636</t>
+          <t>1127865</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1405970</t>
+          <t>1182374</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>646166</t>
+          <t>711338</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646166</t>
+          <t>711338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>646166</t>
+          <t>711338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027231</t>
+          <t>898713</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027231</t>
+          <t>898713</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027231</t>
+          <t>898713</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1673397</t>
+          <t>1610051</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1673397</t>
+          <t>1610051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1673397</t>
+          <t>1610051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
